--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Simpul.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Simpul.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Vertical\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F72DCD-3479-41C9-9881-9D338134C363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -31,7 +37,7 @@
     <t>A*</t>
   </si>
   <si>
-    <t>JPS-BDS-GL-BRC-PPO</t>
+    <t>JPS-GL-BRC-PPO</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -49,8 +55,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,13 +119,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +171,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -191,6 +205,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,9 +240,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -400,11 +416,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,7 +434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -432,7 +448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -440,13 +456,13 @@
         <v>16</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -460,7 +476,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -468,13 +484,13 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -488,7 +504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -496,13 +512,13 @@
         <v>64</v>
       </c>
       <c r="C7">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -516,7 +532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -524,13 +540,13 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -544,7 +560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -552,13 +568,13 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -572,7 +588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -580,13 +596,13 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -600,7 +616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -608,13 +624,13 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -628,7 +644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -636,13 +652,13 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -656,7 +672,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -664,13 +680,13 @@
         <v>16</v>
       </c>
       <c r="C19">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -684,7 +700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -692,13 +708,13 @@
         <v>32</v>
       </c>
       <c r="C21">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -712,7 +728,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -720,13 +736,13 @@
         <v>64</v>
       </c>
       <c r="C23">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -740,7 +756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -748,13 +764,13 @@
         <v>128</v>
       </c>
       <c r="C25">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -768,7 +784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -776,13 +792,13 @@
         <v>16</v>
       </c>
       <c r="C27">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -796,7 +812,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -804,13 +820,13 @@
         <v>32</v>
       </c>
       <c r="C29">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -824,7 +840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -832,13 +848,13 @@
         <v>64</v>
       </c>
       <c r="C31">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -852,7 +868,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -860,13 +876,13 @@
         <v>128</v>
       </c>
       <c r="C33">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -880,7 +896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -888,13 +904,13 @@
         <v>16</v>
       </c>
       <c r="C35">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -908,7 +924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -916,13 +932,13 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -936,7 +952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -944,13 +960,13 @@
         <v>64</v>
       </c>
       <c r="C39">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -964,7 +980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -972,7 +988,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Simpul.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Simpul.xlsx
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Simpul.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Simpul.xlsx
@@ -519,7 +519,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -589,7 +589,7 @@
         <v>64</v>
       </c>
       <c r="C13">
-        <v>406</v>
+        <v>307</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -659,7 +659,7 @@
         <v>128</v>
       </c>
       <c r="C18">
-        <v>1230</v>
+        <v>656</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>16</v>
       </c>
       <c r="C23">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
@@ -799,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -869,7 +869,7 @@
         <v>64</v>
       </c>
       <c r="C33">
-        <v>726</v>
+        <v>481</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -939,7 +939,7 @@
         <v>128</v>
       </c>
       <c r="C38">
-        <v>2683</v>
+        <v>1275</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C43">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1079,7 +1079,7 @@
         <v>32</v>
       </c>
       <c r="C48">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -1149,7 +1149,7 @@
         <v>64</v>
       </c>
       <c r="C53">
-        <v>496</v>
+        <v>318</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -1219,7 +1219,7 @@
         <v>128</v>
       </c>
       <c r="C58">
-        <v>1614</v>
+        <v>811</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -1359,7 +1359,7 @@
         <v>32</v>
       </c>
       <c r="C68">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -1429,7 +1429,7 @@
         <v>64</v>
       </c>
       <c r="C73">
-        <v>390</v>
+        <v>331</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -1499,7 +1499,7 @@
         <v>128</v>
       </c>
       <c r="C78">
-        <v>1206</v>
+        <v>804</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -1639,7 +1639,7 @@
         <v>32</v>
       </c>
       <c r="C88">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D88" t="s">
         <v>12</v>
@@ -1709,7 +1709,7 @@
         <v>64</v>
       </c>
       <c r="C93">
-        <v>555</v>
+        <v>308</v>
       </c>
       <c r="D93" t="s">
         <v>12</v>
@@ -1779,7 +1779,7 @@
         <v>128</v>
       </c>
       <c r="C98">
-        <v>1790</v>
+        <v>664</v>
       </c>
       <c r="D98" t="s">
         <v>12</v>
